--- a/datasets/sample_data/sites.xlsx
+++ b/datasets/sample_data/sites.xlsx
@@ -64,7 +64,7 @@
     <t>Prince Charles Hospital (Macmillan Unit)</t>
   </si>
   <si>
-    <t>Royal Gwent Hospital (Outreach)</t>
+    <t>Royal Glamorgan Hospital (Outreach)</t>
   </si>
   <si>
     <t>Princess of Wales Hospital (Outreach)</t>
@@ -550,10 +550,10 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>51.588</v>
+        <v>51.5728</v>
       </c>
       <c r="I4">
-        <v>-2.999</v>
+        <v>-3.3868</v>
       </c>
     </row>
     <row r="5" spans="1:9">
